--- a/pressure.xlsx
+++ b/pressure.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Andrey\AppData\IdeaProjects\CardioPlot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Andrey\IdeaProjects\CardioPlot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E3A4D0-D850-434F-ADD3-64AF2B93BC9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D791811-F817-4DEF-9CD3-11BA1A2FFB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -422,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F885"/>
+  <dimension ref="A1:F888"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="2" customWidth="1"/>
@@ -15689,6 +15689,57 @@
         <v>67</v>
       </c>
     </row>
+    <row r="886" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A886" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B886" s="1">
+        <v>0.44513888888888886</v>
+      </c>
+      <c r="C886">
+        <v>124</v>
+      </c>
+      <c r="D886">
+        <v>74</v>
+      </c>
+      <c r="E886">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="887" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A887" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B887" s="1">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="C887">
+        <v>135</v>
+      </c>
+      <c r="D887">
+        <v>81</v>
+      </c>
+      <c r="E887">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="888" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A888" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B888" s="1">
+        <v>0.84027777777777779</v>
+      </c>
+      <c r="C888">
+        <v>146</v>
+      </c>
+      <c r="D888">
+        <v>86</v>
+      </c>
+      <c r="E888">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pressure.xlsx
+++ b/pressure.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Andrey\AppData\IdeaProjects\CardioPlot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Andrey\IdeaProjects\CardioPlot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A738BB9-7A55-463F-B0EB-AA013438ADA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554F39F1-3B73-4D0B-A8BF-12AC138CCDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1172"/>
+  <dimension ref="A1:F1200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
@@ -20583,6 +20583,482 @@
         <v>76</v>
       </c>
     </row>
+    <row r="1173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1173" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B1173" s="2">
+        <v>0.71805555555555556</v>
+      </c>
+      <c r="C1173">
+        <v>132</v>
+      </c>
+      <c r="D1173">
+        <v>82</v>
+      </c>
+      <c r="E1173">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1174" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B1174" s="2">
+        <v>0.85972222222222228</v>
+      </c>
+      <c r="C1174">
+        <v>141</v>
+      </c>
+      <c r="D1174">
+        <v>85</v>
+      </c>
+      <c r="E1174">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1175" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B1175" s="2">
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="C1175">
+        <v>156</v>
+      </c>
+      <c r="D1175">
+        <v>99</v>
+      </c>
+      <c r="E1175">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1176" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B1176" s="2">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="C1176">
+        <v>153</v>
+      </c>
+      <c r="D1176">
+        <v>94</v>
+      </c>
+      <c r="E1176">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1177" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B1177" s="2">
+        <v>0.7680555555555556</v>
+      </c>
+      <c r="C1177">
+        <v>156</v>
+      </c>
+      <c r="D1177">
+        <v>97</v>
+      </c>
+      <c r="E1177">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1178" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B1178" s="2">
+        <v>0.98263888888888884</v>
+      </c>
+      <c r="C1178">
+        <v>154</v>
+      </c>
+      <c r="D1178">
+        <v>98</v>
+      </c>
+      <c r="E1178">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1179" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B1179" s="2">
+        <v>0.30277777777777776</v>
+      </c>
+      <c r="C1179">
+        <v>149</v>
+      </c>
+      <c r="D1179">
+        <v>87</v>
+      </c>
+      <c r="E1179">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1180" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B1180" s="2">
+        <v>0.6020833333333333</v>
+      </c>
+      <c r="C1180">
+        <v>141</v>
+      </c>
+      <c r="D1180">
+        <v>86</v>
+      </c>
+      <c r="E1180">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1181" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B1181" s="2">
+        <v>0.87083333333333335</v>
+      </c>
+      <c r="C1181">
+        <v>144</v>
+      </c>
+      <c r="D1181">
+        <v>89</v>
+      </c>
+      <c r="E1181">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1182" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B1182" s="2">
+        <v>0.34236111111111112</v>
+      </c>
+      <c r="C1182">
+        <v>133</v>
+      </c>
+      <c r="D1182">
+        <v>83</v>
+      </c>
+      <c r="E1182">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1183" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B1183" s="2">
+        <v>0.40208333333333335</v>
+      </c>
+      <c r="C1183">
+        <v>147</v>
+      </c>
+      <c r="D1183">
+        <v>85</v>
+      </c>
+      <c r="E1183">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1184" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B1184" s="2">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="C1184">
+        <v>133</v>
+      </c>
+      <c r="D1184">
+        <v>87</v>
+      </c>
+      <c r="E1184">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1185" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B1185" s="2">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="C1185">
+        <v>142</v>
+      </c>
+      <c r="D1185">
+        <v>87</v>
+      </c>
+      <c r="E1185">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1186" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B1186" s="2">
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="C1186">
+        <v>143</v>
+      </c>
+      <c r="D1186">
+        <v>92</v>
+      </c>
+      <c r="E1186">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1187" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B1187" s="2">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="C1187">
+        <v>162</v>
+      </c>
+      <c r="D1187">
+        <v>91</v>
+      </c>
+      <c r="E1187">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1188" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B1188" s="2">
+        <v>0.6958333333333333</v>
+      </c>
+      <c r="C1188">
+        <v>150</v>
+      </c>
+      <c r="D1188">
+        <v>84</v>
+      </c>
+      <c r="E1188">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1189" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B1189" s="2">
+        <v>0.83958333333333335</v>
+      </c>
+      <c r="C1189">
+        <v>148</v>
+      </c>
+      <c r="D1189">
+        <v>79</v>
+      </c>
+      <c r="E1189">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1190" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B1190" s="2">
+        <v>0.21180555555555555</v>
+      </c>
+      <c r="C1190">
+        <v>143</v>
+      </c>
+      <c r="D1190">
+        <v>81</v>
+      </c>
+      <c r="E1190">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1191" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B1191" s="2">
+        <v>0.42569444444444443</v>
+      </c>
+      <c r="C1191">
+        <v>147</v>
+      </c>
+      <c r="D1191">
+        <v>93</v>
+      </c>
+      <c r="E1191">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1192" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B1192" s="2">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="C1192">
+        <v>136</v>
+      </c>
+      <c r="D1192">
+        <v>90</v>
+      </c>
+      <c r="E1192">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1193" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B1193" s="2">
+        <v>0.79374999999999996</v>
+      </c>
+      <c r="C1193">
+        <v>179</v>
+      </c>
+      <c r="D1193">
+        <v>99</v>
+      </c>
+      <c r="E1193">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1194" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B1194" s="2">
+        <v>0.27361111111111114</v>
+      </c>
+      <c r="C1194">
+        <v>144</v>
+      </c>
+      <c r="D1194">
+        <v>86</v>
+      </c>
+      <c r="E1194">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1195" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B1195" s="2">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="C1195">
+        <v>146</v>
+      </c>
+      <c r="D1195">
+        <v>91</v>
+      </c>
+      <c r="E1195">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1196" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B1196" s="2">
+        <v>0.82986111111111116</v>
+      </c>
+      <c r="C1196">
+        <v>145</v>
+      </c>
+      <c r="D1196">
+        <v>89</v>
+      </c>
+      <c r="E1196">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1197" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B1197" s="2">
+        <v>0.25555555555555554</v>
+      </c>
+      <c r="C1197">
+        <v>148</v>
+      </c>
+      <c r="D1197">
+        <v>89</v>
+      </c>
+      <c r="E1197">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1198" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B1198" s="2">
+        <v>0.64444444444444449</v>
+      </c>
+      <c r="C1198">
+        <v>157</v>
+      </c>
+      <c r="D1198">
+        <v>96</v>
+      </c>
+      <c r="E1198">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1199" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B1199" s="2">
+        <v>0.75416666666666665</v>
+      </c>
+      <c r="C1199">
+        <v>154</v>
+      </c>
+      <c r="D1199">
+        <v>92</v>
+      </c>
+      <c r="E1199">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1200" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B1200" s="2">
+        <v>0.98541666666666672</v>
+      </c>
+      <c r="C1200">
+        <v>144</v>
+      </c>
+      <c r="D1200">
+        <v>92</v>
+      </c>
+      <c r="E1200">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pressure.xlsx
+++ b/pressure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Andrey\IdeaProjects\CardioPlot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554F39F1-3B73-4D0B-A8BF-12AC138CCDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37311B56-4AF7-4DBC-9D15-3451518DF532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1200"/>
+  <dimension ref="A1:F1230"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
@@ -20787,7 +20787,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="1185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1185" s="1">
         <v>46130</v>
       </c>
@@ -20804,7 +20804,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="1186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1186" s="1">
         <v>46131</v>
       </c>
@@ -20821,7 +20821,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="1187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1187" s="1">
         <v>46131</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="1188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1188" s="1">
         <v>46131</v>
       </c>
@@ -20855,7 +20855,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="1189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1189" s="1">
         <v>46131</v>
       </c>
@@ -20872,7 +20872,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="1190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1190" s="1">
         <v>46132</v>
       </c>
@@ -20888,8 +20888,11 @@
       <c r="E1190">
         <v>86</v>
       </c>
-    </row>
-    <row r="1191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1190" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1191" s="1">
         <v>46132</v>
       </c>
@@ -20906,7 +20909,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="1192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1192" s="1">
         <v>46132</v>
       </c>
@@ -20923,7 +20926,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="1193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1193" s="1">
         <v>46132</v>
       </c>
@@ -20940,7 +20943,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="1194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1194" s="1">
         <v>46133</v>
       </c>
@@ -20957,7 +20960,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="1195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1195" s="1">
         <v>46133</v>
       </c>
@@ -20974,7 +20977,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="1196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1196" s="1">
         <v>46133</v>
       </c>
@@ -20991,7 +20994,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1197" s="1">
         <v>46134</v>
       </c>
@@ -21008,7 +21011,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="1198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1198" s="1">
         <v>46134</v>
       </c>
@@ -21025,7 +21028,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="1199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1199" s="1">
         <v>46134</v>
       </c>
@@ -21042,7 +21045,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="1200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1200" s="1">
         <v>46134</v>
       </c>
@@ -21057,6 +21060,516 @@
       </c>
       <c r="E1200">
         <v>61</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1201" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B1201" s="2">
+        <v>0.30694444444444446</v>
+      </c>
+      <c r="C1201">
+        <v>144</v>
+      </c>
+      <c r="D1201">
+        <v>87</v>
+      </c>
+      <c r="E1201">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1202" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B1202" s="2">
+        <v>0.46458333333333335</v>
+      </c>
+      <c r="C1202">
+        <v>125</v>
+      </c>
+      <c r="D1202">
+        <v>78</v>
+      </c>
+      <c r="E1202">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1203" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B1203" s="2">
+        <v>0.82916666666666672</v>
+      </c>
+      <c r="C1203">
+        <v>115</v>
+      </c>
+      <c r="D1203">
+        <v>74</v>
+      </c>
+      <c r="E1203">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1204" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B1204" s="2">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1204">
+        <v>133</v>
+      </c>
+      <c r="D1204">
+        <v>78</v>
+      </c>
+      <c r="E1204">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1205" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B1205" s="2">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="C1205">
+        <v>134</v>
+      </c>
+      <c r="D1205">
+        <v>86</v>
+      </c>
+      <c r="E1205">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1206" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B1206" s="2">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="C1206">
+        <v>128</v>
+      </c>
+      <c r="D1206">
+        <v>77</v>
+      </c>
+      <c r="E1206">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1207" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B1207" s="2">
+        <v>0.81458333333333333</v>
+      </c>
+      <c r="C1207">
+        <v>128</v>
+      </c>
+      <c r="D1207">
+        <v>70</v>
+      </c>
+      <c r="E1207">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1208" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B1208" s="2">
+        <v>0.26180555555555557</v>
+      </c>
+      <c r="C1208">
+        <v>137</v>
+      </c>
+      <c r="D1208">
+        <v>81</v>
+      </c>
+      <c r="E1208">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1209" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B1209" s="2">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="C1209">
+        <v>144</v>
+      </c>
+      <c r="D1209">
+        <v>89</v>
+      </c>
+      <c r="E1209">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1210" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B1210" s="2">
+        <v>0.81319444444444444</v>
+      </c>
+      <c r="C1210">
+        <v>142</v>
+      </c>
+      <c r="D1210">
+        <v>90</v>
+      </c>
+      <c r="E1210">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1211" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B1211" s="2">
+        <v>5.4166666666666669E-2</v>
+      </c>
+      <c r="C1211">
+        <v>149</v>
+      </c>
+      <c r="D1211">
+        <v>95</v>
+      </c>
+      <c r="E1211">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1212" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B1212" s="2">
+        <v>0.32777777777777778</v>
+      </c>
+      <c r="C1212">
+        <v>140</v>
+      </c>
+      <c r="D1212">
+        <v>85</v>
+      </c>
+      <c r="E1212">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1213" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B1213" s="2">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="C1213">
+        <v>141</v>
+      </c>
+      <c r="D1213">
+        <v>90</v>
+      </c>
+      <c r="E1213">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1214" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B1214" s="2">
+        <v>0.94861111111111107</v>
+      </c>
+      <c r="C1214">
+        <v>133</v>
+      </c>
+      <c r="D1214">
+        <v>76</v>
+      </c>
+      <c r="E1214">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1215" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B1215" s="2">
+        <v>0.34444444444444444</v>
+      </c>
+      <c r="C1215">
+        <v>132</v>
+      </c>
+      <c r="D1215">
+        <v>85</v>
+      </c>
+      <c r="E1215">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1216" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B1216" s="2">
+        <v>0.54583333333333328</v>
+      </c>
+      <c r="C1216">
+        <v>129</v>
+      </c>
+      <c r="D1216">
+        <v>81</v>
+      </c>
+      <c r="E1216">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1217" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B1217" s="2">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="C1217">
+        <v>132</v>
+      </c>
+      <c r="D1217">
+        <v>83</v>
+      </c>
+      <c r="E1217">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1218" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B1218" s="2">
+        <v>0.86388888888888893</v>
+      </c>
+      <c r="C1218">
+        <v>131</v>
+      </c>
+      <c r="D1218">
+        <v>82</v>
+      </c>
+      <c r="E1218">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1219" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B1219" s="2">
+        <v>0.26597222222222222</v>
+      </c>
+      <c r="C1219">
+        <v>133</v>
+      </c>
+      <c r="D1219">
+        <v>86</v>
+      </c>
+      <c r="E1219">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1220" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B1220" s="2">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="C1220">
+        <v>140</v>
+      </c>
+      <c r="D1220">
+        <v>81</v>
+      </c>
+      <c r="E1220">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1221" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B1221" s="2">
+        <v>0.80763888888888891</v>
+      </c>
+      <c r="C1221">
+        <v>137</v>
+      </c>
+      <c r="D1221">
+        <v>88</v>
+      </c>
+      <c r="E1221">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1222" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B1222" s="2">
+        <v>0.98472222222222228</v>
+      </c>
+      <c r="C1222">
+        <v>156</v>
+      </c>
+      <c r="D1222">
+        <v>97</v>
+      </c>
+      <c r="E1222">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1223" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B1223" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C1223">
+        <v>134</v>
+      </c>
+      <c r="D1223">
+        <v>86</v>
+      </c>
+      <c r="E1223">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1224" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B1224" s="2">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="C1224">
+        <v>133</v>
+      </c>
+      <c r="D1224">
+        <v>81</v>
+      </c>
+      <c r="E1224">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1225" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B1225" s="2">
+        <v>0.75624999999999998</v>
+      </c>
+      <c r="C1225">
+        <v>124</v>
+      </c>
+      <c r="D1225">
+        <v>76</v>
+      </c>
+      <c r="E1225">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1226" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B1226" s="2">
+        <v>0.37222222222222223</v>
+      </c>
+      <c r="C1226">
+        <v>141</v>
+      </c>
+      <c r="D1226">
+        <v>84</v>
+      </c>
+      <c r="E1226">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1227" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B1227" s="2">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="C1227">
+        <v>123</v>
+      </c>
+      <c r="D1227">
+        <v>70</v>
+      </c>
+      <c r="E1227">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1228" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B1228" s="2">
+        <v>0.25416666666666665</v>
+      </c>
+      <c r="C1228">
+        <v>136</v>
+      </c>
+      <c r="D1228">
+        <v>83</v>
+      </c>
+      <c r="E1228">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1229" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B1229" s="2">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="C1229">
+        <v>160</v>
+      </c>
+      <c r="D1229">
+        <v>97</v>
+      </c>
+      <c r="E1229">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1230" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B1230" s="2">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="C1230">
+        <v>147</v>
+      </c>
+      <c r="D1230">
+        <v>96</v>
+      </c>
+      <c r="E1230">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/pressure.xlsx
+++ b/pressure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Andrey\IdeaProjects\CardioPlot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37311B56-4AF7-4DBC-9D15-3451518DF532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E5542E-898C-43AD-9F88-6BC97BE564C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1230"/>
+  <dimension ref="A1:F1251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
@@ -21572,6 +21572,363 @@
         <v>56</v>
       </c>
     </row>
+    <row r="1231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1231" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B1231" s="2">
+        <v>0.22013888888888888</v>
+      </c>
+      <c r="C1231">
+        <v>137</v>
+      </c>
+      <c r="D1231">
+        <v>88</v>
+      </c>
+      <c r="E1231">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1232" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B1232" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1232">
+        <v>126</v>
+      </c>
+      <c r="D1232">
+        <v>67</v>
+      </c>
+      <c r="E1232">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1233" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B1233" s="2">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="C1233">
+        <v>129</v>
+      </c>
+      <c r="D1233">
+        <v>81</v>
+      </c>
+      <c r="E1233">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1234" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B1234" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C1234">
+        <v>121</v>
+      </c>
+      <c r="D1234">
+        <v>72</v>
+      </c>
+      <c r="E1234">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1235" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B1235" s="2">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="C1235">
+        <v>118</v>
+      </c>
+      <c r="D1235">
+        <v>76</v>
+      </c>
+      <c r="E1235">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1236" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B1236" s="2">
+        <v>0.60902777777777772</v>
+      </c>
+      <c r="C1236">
+        <v>133</v>
+      </c>
+      <c r="D1236">
+        <v>81</v>
+      </c>
+      <c r="E1236">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1237" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B1237" s="2">
+        <v>0.8256944444444444</v>
+      </c>
+      <c r="C1237">
+        <v>128</v>
+      </c>
+      <c r="D1237">
+        <v>79</v>
+      </c>
+      <c r="E1237">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1238" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B1238" s="2">
+        <v>0.25138888888888888</v>
+      </c>
+      <c r="C1238">
+        <v>133</v>
+      </c>
+      <c r="D1238">
+        <v>79</v>
+      </c>
+      <c r="E1238">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1239" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B1239" s="2">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C1239">
+        <v>140</v>
+      </c>
+      <c r="D1239">
+        <v>82</v>
+      </c>
+      <c r="E1239">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1240" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B1240" s="2">
+        <v>0.75208333333333333</v>
+      </c>
+      <c r="C1240">
+        <v>139</v>
+      </c>
+      <c r="D1240">
+        <v>90</v>
+      </c>
+      <c r="E1240">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1241" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B1241" s="2">
+        <v>0.20694444444444443</v>
+      </c>
+      <c r="C1241">
+        <v>142</v>
+      </c>
+      <c r="D1241">
+        <v>90</v>
+      </c>
+      <c r="E1241">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1242" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B1242" s="2">
+        <v>0.58263888888888893</v>
+      </c>
+      <c r="C1242">
+        <v>125</v>
+      </c>
+      <c r="D1242">
+        <v>83</v>
+      </c>
+      <c r="E1242">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1243" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B1243" s="2">
+        <v>0.89097222222222228</v>
+      </c>
+      <c r="C1243">
+        <v>113</v>
+      </c>
+      <c r="D1243">
+        <v>71</v>
+      </c>
+      <c r="E1243">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1244" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B1244" s="2">
+        <v>0.37916666666666665</v>
+      </c>
+      <c r="C1244">
+        <v>109</v>
+      </c>
+      <c r="D1244">
+        <v>67</v>
+      </c>
+      <c r="E1244">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1245" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B1245" s="2">
+        <v>0.42152777777777778</v>
+      </c>
+      <c r="C1245">
+        <v>115</v>
+      </c>
+      <c r="D1245">
+        <v>67</v>
+      </c>
+      <c r="E1245">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1246" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B1246" s="2">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="C1246">
+        <v>109</v>
+      </c>
+      <c r="D1246">
+        <v>65</v>
+      </c>
+      <c r="E1246">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1247" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B1247" s="2">
+        <v>0.87222222222222223</v>
+      </c>
+      <c r="C1247">
+        <v>115</v>
+      </c>
+      <c r="D1247">
+        <v>71</v>
+      </c>
+      <c r="E1247">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1248" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B1248" s="2">
+        <v>0.25069444444444444</v>
+      </c>
+      <c r="C1248">
+        <v>139</v>
+      </c>
+      <c r="D1248">
+        <v>79</v>
+      </c>
+      <c r="E1248">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1249" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B1249" s="2">
+        <v>0.53263888888888888</v>
+      </c>
+      <c r="C1249">
+        <v>132</v>
+      </c>
+      <c r="D1249">
+        <v>81</v>
+      </c>
+      <c r="E1249">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1250" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B1250" s="2">
+        <v>0.8208333333333333</v>
+      </c>
+      <c r="C1250">
+        <v>151</v>
+      </c>
+      <c r="D1250">
+        <v>88</v>
+      </c>
+      <c r="E1250">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1251" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B1251" s="2">
+        <v>0.98819444444444449</v>
+      </c>
+      <c r="C1251">
+        <v>142</v>
+      </c>
+      <c r="D1251">
+        <v>87</v>
+      </c>
+      <c r="E1251">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/pressure.xlsx
+++ b/pressure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Andrey\IdeaProjects\CardioPlot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E5542E-898C-43AD-9F88-6BC97BE564C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3D0E1F-18B2-4E62-9FAE-3534797457F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1251"/>
+  <dimension ref="A1:F1312"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
@@ -21929,6 +21929,1016 @@
         <v>68</v>
       </c>
     </row>
+    <row r="1252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1252" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B1252" s="2">
+        <v>0.32222222222222224</v>
+      </c>
+      <c r="C1252">
+        <v>137</v>
+      </c>
+      <c r="D1252">
+        <v>85</v>
+      </c>
+      <c r="E1252">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1253" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B1253" s="2">
+        <v>0.41805555555555557</v>
+      </c>
+      <c r="C1253">
+        <v>133</v>
+      </c>
+      <c r="D1253">
+        <v>79</v>
+      </c>
+      <c r="E1253">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1254" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B1254" s="2">
+        <v>0.77569444444444446</v>
+      </c>
+      <c r="C1254">
+        <v>132</v>
+      </c>
+      <c r="D1254">
+        <v>81</v>
+      </c>
+      <c r="E1254">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1255" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B1255" s="2">
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="C1255">
+        <v>126</v>
+      </c>
+      <c r="D1255">
+        <v>81</v>
+      </c>
+      <c r="E1255">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1256" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B1256" s="2">
+        <v>0.83958333333333335</v>
+      </c>
+      <c r="C1256">
+        <v>133</v>
+      </c>
+      <c r="D1256">
+        <v>79</v>
+      </c>
+      <c r="E1256">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1257" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B1257" s="2">
+        <v>0.26250000000000001</v>
+      </c>
+      <c r="C1257">
+        <v>127</v>
+      </c>
+      <c r="D1257">
+        <v>83</v>
+      </c>
+      <c r="E1257">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1258" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B1258" s="2">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C1258">
+        <v>153</v>
+      </c>
+      <c r="D1258">
+        <v>93</v>
+      </c>
+      <c r="E1258">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1259" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B1259" s="2">
+        <v>0.83472222222222225</v>
+      </c>
+      <c r="C1259">
+        <v>142</v>
+      </c>
+      <c r="D1259">
+        <v>83</v>
+      </c>
+      <c r="E1259">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1260" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1260" s="2">
+        <v>0.21249999999999999</v>
+      </c>
+      <c r="C1260">
+        <v>145</v>
+      </c>
+      <c r="D1260">
+        <v>84</v>
+      </c>
+      <c r="E1260">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1261" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1261" s="2">
+        <v>0.40833333333333333</v>
+      </c>
+      <c r="C1261">
+        <v>123</v>
+      </c>
+      <c r="D1261">
+        <v>79</v>
+      </c>
+      <c r="E1261">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1262" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1262" s="2">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="C1262">
+        <v>118</v>
+      </c>
+      <c r="D1262">
+        <v>73</v>
+      </c>
+      <c r="E1262">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1263" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1263" s="2">
+        <v>0.76944444444444449</v>
+      </c>
+      <c r="C1263">
+        <v>119</v>
+      </c>
+      <c r="D1263">
+        <v>73</v>
+      </c>
+      <c r="E1263">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1264" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B1264" s="2">
+        <v>0.28333333333333333</v>
+      </c>
+      <c r="C1264">
+        <v>133</v>
+      </c>
+      <c r="D1264">
+        <v>82</v>
+      </c>
+      <c r="E1264">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1265" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B1265" s="2">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C1265">
+        <v>127</v>
+      </c>
+      <c r="D1265">
+        <v>75</v>
+      </c>
+      <c r="E1265">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1266" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B1266" s="2">
+        <v>0.94305555555555554</v>
+      </c>
+      <c r="C1266">
+        <v>126</v>
+      </c>
+      <c r="D1266">
+        <v>74</v>
+      </c>
+      <c r="E1266">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1267" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B1267" s="2">
+        <v>0.25624999999999998</v>
+      </c>
+      <c r="C1267">
+        <v>134</v>
+      </c>
+      <c r="D1267">
+        <v>76</v>
+      </c>
+      <c r="E1267">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1268" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B1268" s="2">
+        <v>0.59444444444444444</v>
+      </c>
+      <c r="C1268">
+        <v>132</v>
+      </c>
+      <c r="D1268">
+        <v>82</v>
+      </c>
+      <c r="E1268">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1269" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B1269" s="2">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="C1269">
+        <v>129</v>
+      </c>
+      <c r="D1269">
+        <v>71</v>
+      </c>
+      <c r="E1269">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1270" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B1270" s="2">
+        <v>0.21249999999999999</v>
+      </c>
+      <c r="C1270">
+        <v>141</v>
+      </c>
+      <c r="D1270">
+        <v>87</v>
+      </c>
+      <c r="E1270">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1271" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B1271" s="2">
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="C1271">
+        <v>127</v>
+      </c>
+      <c r="D1271">
+        <v>77</v>
+      </c>
+      <c r="E1271">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1272" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B1272" s="2">
+        <v>0.80138888888888893</v>
+      </c>
+      <c r="C1272">
+        <v>130</v>
+      </c>
+      <c r="D1272">
+        <v>78</v>
+      </c>
+      <c r="E1272">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1273" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1273" s="2">
+        <v>0.30763888888888891</v>
+      </c>
+      <c r="C1273">
+        <v>127</v>
+      </c>
+      <c r="D1273">
+        <v>72</v>
+      </c>
+      <c r="E1273">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1274" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1274" s="2">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="C1274">
+        <v>123</v>
+      </c>
+      <c r="D1274">
+        <v>72</v>
+      </c>
+      <c r="E1274">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1275" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1275" s="2">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="C1275">
+        <v>127</v>
+      </c>
+      <c r="D1275">
+        <v>74</v>
+      </c>
+      <c r="E1275">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1276" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B1276" s="2">
+        <v>0.25833333333333336</v>
+      </c>
+      <c r="C1276">
+        <v>127</v>
+      </c>
+      <c r="D1276">
+        <v>75</v>
+      </c>
+      <c r="E1276">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1277" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B1277" s="2">
+        <v>0.7680555555555556</v>
+      </c>
+      <c r="C1277">
+        <v>134</v>
+      </c>
+      <c r="D1277">
+        <v>79</v>
+      </c>
+      <c r="E1277">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1278" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B1278" s="2">
+        <v>0.99513888888888891</v>
+      </c>
+      <c r="C1278">
+        <v>136</v>
+      </c>
+      <c r="D1278">
+        <v>82</v>
+      </c>
+      <c r="E1278">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1279" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B1279" s="2">
+        <v>0.32708333333333334</v>
+      </c>
+      <c r="C1279">
+        <v>138</v>
+      </c>
+      <c r="D1279">
+        <v>82</v>
+      </c>
+      <c r="E1279">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1280" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B1280" s="2">
+        <v>0.62152777777777779</v>
+      </c>
+      <c r="C1280">
+        <v>120</v>
+      </c>
+      <c r="D1280">
+        <v>72</v>
+      </c>
+      <c r="E1280">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1281" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B1281" s="2">
+        <v>0.91527777777777775</v>
+      </c>
+      <c r="C1281">
+        <v>119</v>
+      </c>
+      <c r="D1281">
+        <v>69</v>
+      </c>
+      <c r="E1281">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1282" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B1282" s="2">
+        <v>0.33124999999999999</v>
+      </c>
+      <c r="C1282">
+        <v>113</v>
+      </c>
+      <c r="D1282">
+        <v>69</v>
+      </c>
+      <c r="E1282">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1283" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B1283" s="2">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="C1283">
+        <v>124</v>
+      </c>
+      <c r="D1283">
+        <v>73</v>
+      </c>
+      <c r="E1283">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1284" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B1284" s="2">
+        <v>0.9194444444444444</v>
+      </c>
+      <c r="C1284">
+        <v>114</v>
+      </c>
+      <c r="D1284">
+        <v>69</v>
+      </c>
+      <c r="E1284">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1285" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B1285" s="2">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="C1285">
+        <v>138</v>
+      </c>
+      <c r="D1285">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1286" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B1286" s="2">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="C1286">
+        <v>124</v>
+      </c>
+      <c r="D1286">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1287" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B1287" s="2">
+        <v>0.79652777777777772</v>
+      </c>
+      <c r="C1287">
+        <v>130</v>
+      </c>
+      <c r="D1287">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1288" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B1288" s="2">
+        <v>0.3659722222222222</v>
+      </c>
+      <c r="C1288">
+        <v>127</v>
+      </c>
+      <c r="D1288">
+        <v>81</v>
+      </c>
+      <c r="E1288">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1289" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B1289" s="2">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="C1289">
+        <v>115</v>
+      </c>
+      <c r="D1289">
+        <v>77</v>
+      </c>
+      <c r="E1289">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1290" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B1290" s="2">
+        <v>0.85555555555555551</v>
+      </c>
+      <c r="C1290">
+        <v>109</v>
+      </c>
+      <c r="D1290">
+        <v>70</v>
+      </c>
+      <c r="E1290">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1291" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1291" s="2">
+        <v>0.39374999999999999</v>
+      </c>
+      <c r="C1291">
+        <v>112</v>
+      </c>
+      <c r="D1291">
+        <v>70</v>
+      </c>
+      <c r="E1291">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1292" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1292" s="2">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="C1292">
+        <v>123</v>
+      </c>
+      <c r="D1292">
+        <v>65</v>
+      </c>
+      <c r="E1292">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1293" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B1293" s="2">
+        <v>0.82013888888888886</v>
+      </c>
+      <c r="C1293">
+        <v>129</v>
+      </c>
+      <c r="D1293">
+        <v>78</v>
+      </c>
+      <c r="E1293">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1294" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1294" s="2">
+        <v>0.21111111111111111</v>
+      </c>
+      <c r="C1294">
+        <v>121</v>
+      </c>
+      <c r="D1294">
+        <v>76</v>
+      </c>
+      <c r="E1294">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1295" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1295" s="2">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="C1295">
+        <v>118</v>
+      </c>
+      <c r="D1295">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1296" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1296" s="2">
+        <v>0.84166666666666667</v>
+      </c>
+      <c r="C1296">
+        <v>120</v>
+      </c>
+      <c r="D1296">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1297" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1297" s="2">
+        <v>0.37013888888888891</v>
+      </c>
+      <c r="C1297">
+        <v>126</v>
+      </c>
+      <c r="D1297">
+        <v>77</v>
+      </c>
+      <c r="E1297">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1298" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1298" s="2">
+        <v>0.68819444444444444</v>
+      </c>
+      <c r="C1298">
+        <v>126</v>
+      </c>
+      <c r="D1298">
+        <v>80</v>
+      </c>
+      <c r="E1298">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1299" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1299" s="2">
+        <v>0.29305555555555557</v>
+      </c>
+      <c r="C1299">
+        <v>128</v>
+      </c>
+      <c r="D1299">
+        <v>79</v>
+      </c>
+      <c r="E1299">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1300" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1300" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C1300">
+        <v>130</v>
+      </c>
+      <c r="D1300">
+        <v>71</v>
+      </c>
+      <c r="E1300">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1301" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1301" s="2">
+        <v>0.7319444444444444</v>
+      </c>
+      <c r="C1301">
+        <v>132</v>
+      </c>
+      <c r="D1301">
+        <v>79</v>
+      </c>
+      <c r="E1301">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1302" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1302" s="2">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="C1302">
+        <v>139</v>
+      </c>
+      <c r="D1302">
+        <v>80</v>
+      </c>
+      <c r="E1302">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1303" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1303" s="2">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="C1303">
+        <v>120</v>
+      </c>
+      <c r="D1303">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1304" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1304" s="2">
+        <v>0.83125000000000004</v>
+      </c>
+      <c r="C1304">
+        <v>124</v>
+      </c>
+      <c r="D1304">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1305" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1305" s="2">
+        <v>0.50486111111111109</v>
+      </c>
+      <c r="C1305">
+        <v>127</v>
+      </c>
+      <c r="D1305">
+        <v>77</v>
+      </c>
+      <c r="E1305">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1306" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1306" s="2">
+        <v>0.8618055555555556</v>
+      </c>
+      <c r="C1306">
+        <v>125</v>
+      </c>
+      <c r="D1306">
+        <v>75</v>
+      </c>
+      <c r="E1306">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1307" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1307" s="2">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="C1307">
+        <v>130</v>
+      </c>
+      <c r="D1307">
+        <v>75</v>
+      </c>
+      <c r="E1307">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1308" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1308" s="2">
+        <v>0.55625000000000002</v>
+      </c>
+      <c r="C1308">
+        <v>129</v>
+      </c>
+      <c r="D1308">
+        <v>78</v>
+      </c>
+      <c r="E1308">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1309" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B1309" s="2">
+        <v>0.87222222222222223</v>
+      </c>
+      <c r="C1309">
+        <v>127</v>
+      </c>
+      <c r="D1309">
+        <v>77</v>
+      </c>
+      <c r="E1309">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1310" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1310" s="2">
+        <v>0.20624999999999999</v>
+      </c>
+      <c r="C1310">
+        <v>133</v>
+      </c>
+      <c r="D1310">
+        <v>80</v>
+      </c>
+      <c r="E1310">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1311" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1311" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C1311">
+        <v>124</v>
+      </c>
+      <c r="D1311">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1312" s="1">
+        <v>46173</v>
+      </c>
+      <c r="B1312" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1312">
+        <v>140</v>
+      </c>
+      <c r="D1312">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
